--- a/data/intermediate/tasa_objetivo.xlsx
+++ b/data/intermediate/tasa_objetivo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6698" uniqueCount="6698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6700" uniqueCount="6700">
   <si>
     <t>fecha</t>
   </si>
@@ -20108,6 +20108,12 @@
   </si>
   <si>
     <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
   </si>
 </sst>
 </file>
@@ -20439,7 +20445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6697"/>
+  <dimension ref="A1:B6699"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -74018,6 +74024,22 @@
         <v>6.5</v>
       </c>
     </row>
+    <row r="6698" spans="1:2">
+      <c r="A6698" t="s">
+        <v>6698</v>
+      </c>
+      <c r="B6698">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="6699" spans="1:2">
+      <c r="A6699" t="s">
+        <v>6699</v>
+      </c>
+      <c r="B6699">
+        <v>6.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
